--- a/SwapVol_OIS.xlsx
+++ b/SwapVol_OIS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruger\PycharmProjects\MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E52776AE-33DE-4AE5-ACC0-F39C4CE3C8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836A357D-D11C-4898-B225-C3E71944FB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{E6FCDBC5-45A1-406F-880C-4A97ABFD0D39}"/>
   </bookViews>
@@ -457,7 +457,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
